--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -431,63 +431,63 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>0js8u60b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>ripawyyS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,69 +425,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A10"/>
+  <dimension ref="A2:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>0js8u60b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>ripawyyS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>zkPwWhT1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A19"/>
+  <dimension ref="A2:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -491,69 +491,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OCd990al</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CKcVGr7E</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>pSpI7vU0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>hhlQ5IbD</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>ObHze1pe</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>8nivFMyR</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ppvl45N8</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>KQAqguF7</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xrJSdNFr</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A10"/>
+  <dimension ref="A2:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -491,6 +491,62 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,125 +425,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A18"/>
+  <dimension ref="A2:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>ppvl45N8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>OCd990al</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>xrJSdNFr</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>hhlQ5IbD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>SU02594U</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>p6XSLUlB</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,15 +425,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>ppvl45N8</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>x2fvnkud</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>hernandez lucas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>dMyiR1D8</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>kimpembe presnel</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>xfW2M1Tt</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ramos goncalo</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>dSDrHenE</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>gueguin axel</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4hOup61a</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>jullien christopher</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +543,16 @@
           <t>pSpI7vU0</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +560,16 @@
           <t>CKcVGr7E</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +577,16 @@
           <t>KQAqguF7</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +594,16 @@
           <t>OCd990al</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +611,16 @@
           <t>ObHze1pe</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +628,16 @@
           <t>8nivFMyR</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +645,16 @@
           <t>xrJSdNFr</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +662,16 @@
           <t>hhlQ5IbD</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -497,6 +679,16 @@
           <t>vmgpBDzg</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -504,6 +696,16 @@
           <t>bk9o9i55</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -511,6 +713,16 @@
           <t>6FCg7VZH</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -518,6 +730,16 @@
           <t>tYQyK8JN</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -525,6 +747,16 @@
           <t>IgtCPCkn</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -532,6 +764,16 @@
           <t>SU02594U</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -539,6 +781,16 @@
           <t>ChZKNjKb</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -546,6 +798,16 @@
           <t>p6XSLUlB</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -553,6 +815,16 @@
           <t>6ZfxDZ5t</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,143 +425,233 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_3</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>x2fvnkud</t>
+          <t>2yi87XSs</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>hernandez lucas</t>
+          <t>coulibaly mamadou</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>dMyiR1D8</t>
+          <t>EJpPkLtD</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>kimpembe presnel</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>xfW2M1Tt</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ramos goncalo</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>dSDrHenE</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>gueguin axel</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>4hOup61a</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>jullien christopher</t>
-        </is>
-      </c>
+          <t>diop edan</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>QiEHuYPM</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>allevinah jim</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>WdtzR8gp</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>kalumba justin noel</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>UVRm5Kjk</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>bentaleb nabil</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AmAtkgFg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>gomes angel</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>neNU9A9F</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ismaily</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>zsH7aMfI</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>umtiti samuel</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>xGol69CN</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>zedadka akim</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>vqK5oQ8e</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>zhegrova edon</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4GZwFq7E</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>logbo andy elysee</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -570,261 +660,12 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>KQAqguF7</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>OCd990al</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>ObHze1pe</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8nivFMyR</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>xrJSdNFr</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>hhlQ5IbD</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>vmgpBDzg</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>bk9o9i55</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6FCg7VZH</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>tYQyK8JN</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IgtCPCkn</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>SU02594U</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,239 +425,309 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
-        </is>
-      </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_home_5</t>
+          <t>id_player_miss_away_3</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_home_5</t>
+          <t>player_name_miss_away_3</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_home_6</t>
+          <t>id_player_miss_away_4</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_home_6</t>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2yi87XSs</t>
+          <t>rczCYkgC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>coulibaly mamadou</t>
+          <t>abdul samed salis</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EJpPkLtD</t>
+          <t>KIP4iWK5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>diop edan</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>cabot jimmy</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>f3mqZ2x6</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>el aynaoui neil</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>IJr88643</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>spierings stijn</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>pQ5GqXFF</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>locko bradley</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>QiEHuYPM</t>
+          <t>hYtVzJ13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>allevinah jim</t>
+          <t>centonze fabien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>WdtzR8gp</t>
+          <t>GCkY7Wy8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>kalumba justin noel</t>
+          <t>ganago igniatius</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UVRm5Kjk</t>
+          <t>l2t9fvR7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>bentaleb nabil</t>
+          <t>mahamoud adel</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AmAtkgFg</t>
+          <t>0t5Mjaa6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>gomes angel</t>
+          <t>mollet florent</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>neNU9A9F</t>
+          <t>vJSrWUkm</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ismaily</t>
+          <t>agouzoul saad</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>zsH7aMfI</t>
+          <t>fo9YVp8o</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>umtiti samuel</t>
+          <t>akpa clement</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>xGol69CN</t>
+          <t>C2z1xx12</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>zedadka akim</t>
+          <t>camara ousmane</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>vqK5oQ8e</t>
+          <t>2TkiOPy5</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>zhegrova edon</t>
+          <t>mensah gideon</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>UZG5ZtWh</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>n gatta ange</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4GZwFq7E</t>
+          <t>pEEqeFXD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>logbo andy elysee</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+          <t>boga jeremie</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8fA5XmQC</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>diop sofiane</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KdLy7rKC</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>laborde gaetan</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ny2HpVKp</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>moffi teremas</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -666,6 +736,363 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>tvY8ZVkb</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>delaine thomas</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>rcZfwzkD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sahi dion</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hjJue7Qt</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>lukovic milos</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CngQQtwt</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>alemdar dogan</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0S6Hz5ji</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>carboni valentin</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MkgjOoBG</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>kone ismael</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2TItKacj</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>nadir bilal</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>rwGnwOU5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ruiz pedro</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>63FSiIkD</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>daramy mohammed</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>MoRIjLE2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>kone abdoul</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>vmgpBDzg</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bk9o9i55</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>SU02594U</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ChZKNjKb</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>p6XSLUlB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,15 +425,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>vmgpBDzg</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>tvY8ZVkb</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>delaine thomas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>rcZfwzkD</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sahi dion</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hjJue7Qt</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>lukovic milos</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +503,12 @@
           <t>bk9o9i55</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +516,12 @@
           <t>6FCg7VZH</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +529,12 @@
           <t>tYQyK8JN</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +542,12 @@
           <t>IgtCPCkn</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +555,12 @@
           <t>SU02594U</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +568,12 @@
           <t>ChZKNjKb</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +581,12 @@
           <t>p6XSLUlB</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +594,12 @@
           <t>6ZfxDZ5t</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,181 +425,630 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>tvY8ZVkb</t>
+          <t>pQ5GqXFF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>delaine thomas</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>rcZfwzkD</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>sahi dion</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>hjJue7Qt</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>lukovic milos</t>
-        </is>
-      </c>
+          <t>locko bradley</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>dSDrHenE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>gueguin axel</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4hOup61a</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>jullien christopher</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hYtVzJ13</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>centonze fabien</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>GCkY7Wy8</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ganago igniatius</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>l2t9fvR7</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>mahamoud adel</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0t5Mjaa6</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>mollet florent</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>MkgjOoBG</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>kone ismael</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2TItKacj</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>nadir bilal</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>boBGHitI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>camara lamine</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2yi87XSs</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>coulibaly mamadou</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>rczCYkgC</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>abdul samed salis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>KIP4iWK5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cabot jimmy</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>f3mqZ2x6</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>el aynaoui neil</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>EJpPkLtD</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>diop edan</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>SU02594U</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>QiEHuYPM</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>allevinah jim</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>WdtzR8gp</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>kalumba justin noel</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>pEEqeFXD</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>boga jeremie</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>8fA5XmQC</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>diop sofiane</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>KdLy7rKC</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>laborde gaetan</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ny2HpVKp</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>moffi teremas</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+          <t>ChZKNjKb</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4GZwFq7E</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>logbo andy elysee</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>vJSrWUkm</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>agouzoul saad</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>fo9YVp8o</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>akpa clement</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2TkiOPy5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>mensah gideon</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>UZG5ZtWh</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>n gatta ange</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>xCwPADx0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>onaiwu ado</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>p6XSLUlB</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>63FSiIkD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>daramy mohammed</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MoRIjLE2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>kone abdoul</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CngQQtwt</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>alemdar dogan</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
           <t>6ZfxDZ5t</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UVRm5Kjk</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>bentaleb nabil</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AmAtkgFg</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>gomes angel</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>x2fvnkud</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>hernandez lucas</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>dMyiR1D8</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>kimpembe presnel</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>xfW2M1Tt</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ramos goncalo</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>neNU9A9F</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ismaily</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>zsH7aMfI</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>umtiti samuel</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>xGol69CN</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>zedadka akim</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,54 +451,54 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_4</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_4</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_5</t>
@@ -527,35 +527,85 @@
       <c r="U1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pQ5GqXFF</t>
+          <t>boBGHitI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>locko bradley</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>camara lamine</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2yi87XSs</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>coulibaly mamadou</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>EJpPkLtD</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>diop edan</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>KIP4iWK5</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>cabot jimmy</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>f3mqZ2x6</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>el aynaoui neil</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>CSjPEukJ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>machado deiver</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -564,487 +614,320 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dSDrHenE</t>
+          <t>QiEHuYPM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gueguin axel</t>
+          <t>allevinah jim</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4hOup61a</t>
+          <t>WdtzR8gp</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>jullien christopher</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>hYtVzJ13</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>centonze fabien</t>
-        </is>
-      </c>
+          <t>kalumba justin noel</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>GCkY7Wy8</t>
+          <t>pEEqeFXD</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ganago igniatius</t>
+          <t>boga jeremie</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>l2t9fvR7</t>
+          <t>8fA5XmQC</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>mahamoud adel</t>
+          <t>diop sofiane</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0t5Mjaa6</t>
+          <t>KdLy7rKC</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>mollet florent</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+          <t>laborde gaetan</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ny2HpVKp</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>moffi teremas</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+          <t>ChZKNjKb</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4GZwFq7E</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>logbo andy elysee</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>MkgjOoBG</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>kone ismael</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2TItKacj</t>
+          <t>vJSrWUkm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>nadir bilal</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+          <t>agouzoul saad</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fo9YVp8o</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>akpa clement</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2TkiOPy5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>mensah gideon</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>UZG5ZtWh</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>n gatta ange</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>xCwPADx0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>onaiwu ado</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>boBGHitI</t>
+          <t>4nBZRS2T</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>camara lamine</t>
+          <t>akieme sergio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2yi87XSs</t>
+          <t>63FSiIkD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>coulibaly mamadou</t>
+          <t>daramy mohammed</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>rczCYkgC</t>
+          <t>MoRIjLE2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>abdul samed salis</t>
+          <t>kone abdoul</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>KIP4iWK5</t>
+          <t>CngQQtwt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cabot jimmy</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>f3mqZ2x6</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>el aynaoui neil</t>
-        </is>
-      </c>
+          <t>alemdar dogan</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>EJpPkLtD</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>diop edan</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>QiEHuYPM</t>
+          <t>zB5OlUKE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>allevinah jim</t>
+          <t>bakker mitchel</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>WdtzR8gp</t>
+          <t>UVRm5Kjk</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>kalumba justin noel</t>
+          <t>bentaleb nabil</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>pEEqeFXD</t>
+          <t>AmAtkgFg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>boga jeremie</t>
+          <t>gomes angel</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8fA5XmQC</t>
+          <t>x2fvnkud</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>diop sofiane</t>
+          <t>hernandez lucas</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>KdLy7rKC</t>
+          <t>dMyiR1D8</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>laborde gaetan</t>
+          <t>kimpembe presnel</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ny2HpVKp</t>
+          <t>xfW2M1Tt</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>moffi teremas</t>
+          <t>ramos goncalo</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4GZwFq7E</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>logbo andy elysee</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>vJSrWUkm</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>agouzoul saad</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>fo9YVp8o</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>akpa clement</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2TkiOPy5</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>mensah gideon</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>UZG5ZtWh</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>n gatta ange</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>xCwPADx0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>onaiwu ado</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>63FSiIkD</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>daramy mohammed</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MoRIjLE2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>kone abdoul</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>CngQQtwt</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>alemdar dogan</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>UVRm5Kjk</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>bentaleb nabil</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>AmAtkgFg</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>gomes angel</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>x2fvnkud</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>hernandez lucas</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>dMyiR1D8</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>kimpembe presnel</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>xfW2M1Tt</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>ramos goncalo</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>neNU9A9F</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>ismaily</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>zsH7aMfI</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>umtiti samuel</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>xGol69CN</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>zedadka akim</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A10"/>
+  <dimension ref="A2:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -491,6 +491,69 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0K4Ww3Ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>noOg1c8K</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>v39B1623</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6V4QeyWs</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,134 +425,497 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A19"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vsYzkTIc</t>
-        </is>
-      </c>
+          <t>hCffxjZi</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CngQQtwt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>alemdar dogan</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>lIN7BM8b</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ostigard leo</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>bkWk025d</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>chotard joris</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>dSDrHenE</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>gueguin axel</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4hOup61a</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>jullien christopher</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>ERFuKxAR</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>kouyate boubakar</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>AX8IYJcC</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>mincarelli lucas</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>G8o32H2s</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>sainte luce theo</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0dMqm7mA</t>
+          <t>M51AY7YG</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MiH8I5Na</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>castelletto jean charles</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>hYtVzJ13</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>centonze fabien</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4nBZRS2T</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>akieme sergio</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>63FSiIkD</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>daramy mohammed</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>MoRIjLE2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>kone abdoul</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>GCkY7Wy8</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ganago igniatius</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>l2t9fvR7</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>mahamoud adel</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0t5Mjaa6</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>mollet florent</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CGH7Enso</t>
-        </is>
-      </c>
+          <t>E3tkRPQj</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ye5BXk1R</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bellaarouch alaa</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>tvY8ZVkb</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>delaine thomas</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>QiEHuYPM</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>allevinah jim</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>WdtzR8gp</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>kalumba justin noel</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>SdIAUhSt</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>lopy joseph</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>rcZfwzkD</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>sahi dion</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>hjJue7Qt</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>lukovic milos</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8MPiooIM</t>
-        </is>
-      </c>
+          <t>fJaIWo3T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>d6nU7y6U</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>magri frank</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4GZwFq7E</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>logbo andy elysee</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>M51AY7YG</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>E3tkRPQj</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>fJaIWo3T</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
           <t>Qw81zU34</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>0K4Ww3Ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>fiy8wfGD</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>noOg1c8K</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>v39B1623</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>6V4QeyWs</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>6HPisxHl</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>nTCJapXF</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>EsTauGo1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>S66OuPup</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>KIP4iWK5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cabot jimmy</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>f3mqZ2x6</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>el aynaoui neil</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>rsiloRPO</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>nuamah ernest</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>jgaGiVOl</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>tagliafico nicolas</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,134 +425,730 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A19"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0K4Ww3Ad</t>
-        </is>
-      </c>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>UZDgIuNN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>haraldsson hakon arnar</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>neNU9A9F</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ismaily</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OADlCrGQ</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>mbappe ethan</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>zsH7aMfI</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>umtiti samuel</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Ye5BXk1R</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>bellaarouch alaa</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>tvY8ZVkb</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>delaine thomas</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>rcZfwzkD</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>sahi dion</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>hjJue7Qt</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>lukovic milos</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>ARPvetaS</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wiley caleb</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fiy8wfGD</t>
-        </is>
-      </c>
+          <t>noOg1c8K</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CngQQtwt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>alemdar dogan</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>KIP4iWK5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>cabot jimmy</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>noOg1c8K</t>
-        </is>
-      </c>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4nBZRS2T</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>akieme sergio</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>63FSiIkD</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>daramy mohammed</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>YywLL7YO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>gabriel moscardo</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>MoRIjLE2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>kone abdoul</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>GQMMQo6m</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>asensio marco</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>WScbdXmL</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>donnarumma gianluigi</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>MqFBkBsp</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>hakimi achraf</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>x2fvnkud</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>hernandez lucas</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>dMyiR1D8</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>kimpembe presnel</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>xfW2M1Tt</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>ramos goncalo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v39B1623</t>
-        </is>
-      </c>
+          <t>6V4QeyWs</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2yi87XSs</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>coulibaly mamadou</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EJpPkLtD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>diop edan</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>C0xxPBa2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>majecki radoslaw</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4GZwFq7E</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>logbo andy elysee</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6V4QeyWs</t>
-        </is>
-      </c>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>WdtzR8gp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>kalumba justin noel</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SdIAUhSt</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>lopy joseph</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>hYtVzJ13</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>centonze fabien</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0t5Mjaa6</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>mollet florent</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>roG6AGUf</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>mostafa mohamed</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6HPisxHl</t>
-        </is>
-      </c>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M3LA15Bh</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>lees melou pierre</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>pQ5GqXFF</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>locko bradley</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>rNvzndzO</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>wasbauer nicolas</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nTCJapXF</t>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>bkWk025d</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>chotard joris</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>dSDrHenE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>gueguin axel</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4hOup61a</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>jullien christopher</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ERFuKxAR</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>kouyate boubakar</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>vJSrWUkm</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>agouzoul saad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2TkiOPy5</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>mensah gideon</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>UZG5ZtWh</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>n gatta ange</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>AX8IYJcC</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>mincarelli lucas</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>G8o32H2s</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>sainte luce theo</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EsTauGo1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
           <t>S66OuPup</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>MRfkjXaJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>zBdshgV6</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>v3PZcqJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>xb7MlutC</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>tvuaMWgc</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>merlin quentin</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2TItKacj</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>nadir bilal</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,15 +425,189 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A19"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>MRfkjXaJ</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>vJSrWUkm</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>agouzoul saad</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>W0j88M7O</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>coulibaly lasso</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>UZG5ZtWh</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>n gatta ange</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>M3LA15Bh</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>lees melou pierre</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>pQ5GqXFF</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>locko bradley</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +615,68 @@
           <t>zBdshgV6</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GQMMQo6m</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>asensio marco</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>x2fvnkud</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>hernandez lucas</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>dMyiR1D8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>kimpembe presnel</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CngQQtwt</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>alemdar dogan</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>xfW2M1Tt</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ramos goncalo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +684,84 @@
           <t>v3PZcqJP</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KIP4iWK5</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>cabot jimmy</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>z1MBQMNN</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>danso kevin</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2qEVnrLJ</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ojediran hamzat</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>KdLy7rKC</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>laborde gaetan</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ny2HpVKp</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>moffi teremas</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>rmhmN1WA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>satriano martin</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>n5LaWeHr</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>sanson morgan</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +769,76 @@
           <t>xb7MlutC</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4GZwFq7E</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>logbo andy elysee</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>UVRm5Kjk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>bentaleb nabil</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>UZDgIuNN</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>haraldsson hakon arnar</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>neNU9A9F</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ismaily</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2Nyle1h2</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>mukau ngal ayel</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>zsH7aMfI</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>umtiti samuel</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +846,100 @@
           <t>lxyu7Met</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2yi87XSs</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>coulibaly mamadou</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EJpPkLtD</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>diop edan</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>C0xxPBa2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>majecki radoslaw</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Y7pbUJA4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>al tamari mousa suleiman</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bkWk025d</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>chotard joris</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4hOup61a</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>jullien christopher</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>OEsM5Dqs</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>maamma othmane</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>G8o32H2s</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>sainte luce theo</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>IFhobcS1</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>sylla issiaga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +947,36 @@
           <t>bDeVnJAO</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rNvzndzO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>wasbauer nicolas</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +984,84 @@
           <t>p4Um50Qh</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>f9CImc7o</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ekomie jacques</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>WdtzR8gp</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>kalumba justin noel</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SdIAUhSt</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>lopy joseph</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>YywLL7YO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>gabriel moscardo</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>MoRIjLE2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>kone abdoul</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>YPPpPcRe</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>sabanovic halid</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>zBgW9dak</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>okumu joseph</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +1069,92 @@
           <t>zZA5hNtm</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>hYtVzJ13</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>centonze fabien</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>GCkY7Wy8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ganago igniatius</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AiotaxUt</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>guirassy bahereba</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>KKGaeL7f</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>briancon anthony</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>by5QHeY8</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>macon yvann</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0t5Mjaa6</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>mollet florent</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>OlWkr4He</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>monconduit thomas</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>vswx9zEb</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>wadji ibrahima</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,67 +1162,98 @@
           <t>Ee8YgF0f</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>xYNVFHvB</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>z9REJaun</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Wf14adfU</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8Kp3c9Oq</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IHSe3ve5</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>rZUMHwAb</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>WhWcJjo3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>4nvCemgd</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>OUcd1IPH</t>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ye5BXk1R</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>bellaarouch alaa</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>tvY8ZVkb</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>delaine thomas</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>rcZfwzkD</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>sahi dion</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>tvuaMWgc</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>merlin quentin</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>jXMIit0S</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>moumbagna faris</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hjJue7Qt</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lukovic milos</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2TItKacj</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>nadir bilal</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>l08EAP2Q</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>rabiot adrien</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>ARPvetaS</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>wiley caleb</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,34 +461,34 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
-        </is>
-      </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
@@ -501,101 +501,59 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_4</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_6</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_6</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MRfkjXaJ</t>
+          <t>bDeVnJAO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>vJSrWUkm</t>
+          <t>rNvzndzO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>agouzoul saad</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>W0j88M7O</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>coulibaly lasso</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>UZG5ZtWh</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>n gatta ange</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>M3LA15Bh</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>lees melou pierre</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>pQ5GqXFF</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>locko bradley</t>
-        </is>
-      </c>
+          <t>wasbauer nicolas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -606,654 +564,293 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zBdshgV6</t>
+          <t>p4Um50Qh</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GQMMQo6m</t>
+          <t>f9CImc7o</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>asensio marco</t>
+          <t>ekomie jacques</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>x2fvnkud</t>
+          <t>WdtzR8gp</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>hernandez lucas</t>
+          <t>kalumba justin noel</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>dMyiR1D8</t>
+          <t>SdIAUhSt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>kimpembe presnel</t>
+          <t>lopy joseph</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CngQQtwt</t>
+          <t>YPPpPcRe</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>alemdar dogan</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>sabanovic halid</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>YywLL7YO</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>gabriel moscardo</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>xfW2M1Tt</t>
+          <t>MoRIjLE2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ramos goncalo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+          <t>kone abdoul</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>zBgW9dak</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>okumu joseph</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>v3PZcqJP</t>
+          <t>zZA5hNtm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KIP4iWK5</t>
+          <t>hYtVzJ13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cabot jimmy</t>
+          <t>centonze fabien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>z1MBQMNN</t>
+          <t>G6Icx4DR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>danso kevin</t>
+          <t>duverne jean kevin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2qEVnrLJ</t>
+          <t>GCkY7Wy8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ojediran hamzat</t>
+          <t>ganago igniatius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>KdLy7rKC</t>
+          <t>AiotaxUt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>laborde gaetan</t>
+          <t>guirassy bahereba</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ny2HpVKp</t>
+          <t>KKGaeL7f</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>moffi teremas</t>
+          <t>briancon anthony</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>rmhmN1WA</t>
+          <t>by5QHeY8</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>satriano martin</t>
+          <t>macon yvann</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>n5LaWeHr</t>
+          <t>OlWkr4He</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>sanson morgan</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+          <t>monconduit thomas</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0vxfG1Jf</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>kadewere tino</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0t5Mjaa6</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>mollet florent</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>vswx9zEb</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>wadji ibrahima</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xb7MlutC</t>
+          <t>Ee8YgF0f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4GZwFq7E</t>
+          <t>Ye5BXk1R</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>logbo andy elysee</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>bellaarouch alaa</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>tvY8ZVkb</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>delaine thomas</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>rcZfwzkD</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>sahi dion</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>UVRm5Kjk</t>
+          <t>hjJue7Qt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>bentaleb nabil</t>
+          <t>lukovic milos</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>UZDgIuNN</t>
+          <t>tvuaMWgc</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>haraldsson hakon arnar</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>merlin quentin</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>jXMIit0S</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>moumbagna faris</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>neNU9A9F</t>
+          <t>2TItKacj</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ismaily</t>
+          <t>nadir bilal</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2Nyle1h2</t>
+          <t>ARPvetaS</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>mukau ngal ayel</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>zsH7aMfI</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>umtiti samuel</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2yi87XSs</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>coulibaly mamadou</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>EJpPkLtD</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>diop edan</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>C0xxPBa2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>majecki radoslaw</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Y7pbUJA4</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>al tamari mousa suleiman</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bkWk025d</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>chotard joris</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>4hOup61a</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>jullien christopher</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>OEsM5Dqs</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>maamma othmane</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>G8o32H2s</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>sainte luce theo</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>IFhobcS1</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>sylla issiaga</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>rNvzndzO</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>wasbauer nicolas</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>f9CImc7o</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ekomie jacques</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>WdtzR8gp</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>kalumba justin noel</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SdIAUhSt</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>lopy joseph</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>YywLL7YO</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>gabriel moscardo</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>MoRIjLE2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>kone abdoul</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>YPPpPcRe</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>sabanovic halid</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>zBgW9dak</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>okumu joseph</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>hYtVzJ13</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>centonze fabien</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>GCkY7Wy8</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ganago igniatius</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>AiotaxUt</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>guirassy bahereba</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>KKGaeL7f</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>briancon anthony</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>by5QHeY8</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>macon yvann</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0t5Mjaa6</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>mollet florent</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>OlWkr4He</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>monconduit thomas</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>vswx9zEb</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>wadji ibrahima</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Ye5BXk1R</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>bellaarouch alaa</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>tvY8ZVkb</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>delaine thomas</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>rcZfwzkD</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>sahi dion</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>tvuaMWgc</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>merlin quentin</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>jXMIit0S</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>moumbagna faris</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hjJue7Qt</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lukovic milos</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2TItKacj</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>nadir bilal</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+          <t>wiley caleb</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
         <is>
           <t>l08EAP2Q</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>rabiot adrien</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>ARPvetaS</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>wiley caleb</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,398 +461,810 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_4</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_5</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_5</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_6</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_6</t>
-        </is>
-      </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_4</t>
+          <t>id_player_miss_away_5</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_away_4</t>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_8</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_8</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bDeVnJAO</t>
+          <t>xYNVFHvB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>rNvzndzO</t>
+          <t>MkgjOoBG</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>wasbauer nicolas</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+          <t>kone ismael</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>jXMIit0S</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>moumbagna faris</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2TItKacj</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>nadir bilal</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>tSVHHLjn</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>cherif sidiki</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ba2ejA41</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>dieng bamba cheikh dieng</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>WdtzR8gp</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>kalumba justin noel</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>SdIAUhSt</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>lopy joseph</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p4Um50Qh</t>
+          <t>z9REJaun</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>f9CImc7o</t>
+          <t>KKGaeL7f</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ekomie jacques</t>
+          <t>briancon anthony</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>WdtzR8gp</t>
+          <t>67mIaVqd</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>kalumba justin noel</t>
+          <t>cornud pierre</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SdIAUhSt</t>
+          <t>by5QHeY8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>lopy joseph</t>
+          <t>macon yvann</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>YPPpPcRe</t>
+          <t>vJSrWUkm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>sabanovic halid</t>
+          <t>agouzoul saad</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>YywLL7YO</t>
+          <t>W0j88M7O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>gabriel moscardo</t>
+          <t>coulibaly lasso</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>MoRIjLE2</t>
+          <t>UZG5ZtWh</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>kone abdoul</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>zBgW9dak</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>okumu joseph</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+          <t>n gatta ange</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>OlWkr4He</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>monconduit thomas</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>vswx9zEb</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wadji ibrahima</t>
+        </is>
+      </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zZA5hNtm</t>
+          <t>Wf14adfU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>hYtVzJ13</t>
+          <t>UVRm5Kjk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>centonze fabien</t>
+          <t>bentaleb nabil</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>G6Icx4DR</t>
+          <t>UZDgIuNN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>duverne jean kevin</t>
+          <t>haraldsson hakon arnar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GCkY7Wy8</t>
+          <t>OADlCrGQ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ganago igniatius</t>
+          <t>mbappe ethan</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AiotaxUt</t>
+          <t>rNvzndzO</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>guirassy bahereba</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>KKGaeL7f</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>briancon anthony</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>by5QHeY8</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>macon yvann</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>OlWkr4He</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>monconduit thomas</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0vxfG1Jf</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>kadewere tino</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0t5Mjaa6</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>mollet florent</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>vswx9zEb</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>wadji ibrahima</t>
-        </is>
-      </c>
+          <t>wasbauer nicolas</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ye5BXk1R</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>bellaarouch alaa</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>tvY8ZVkb</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>delaine thomas</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>rcZfwzkD</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>sahi dion</t>
-        </is>
-      </c>
+          <t>8Kp3c9Oq</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>hjJue7Qt</t>
+          <t>2yi87XSs</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>lukovic milos</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>tvuaMWgc</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>merlin quentin</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>jXMIit0S</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>moumbagna faris</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2TItKacj</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>nadir bilal</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>ARPvetaS</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>wiley caleb</t>
-        </is>
-      </c>
+          <t>coulibaly mamadou</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>l08EAP2Q</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>rabiot adrien</t>
-        </is>
-      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>hYtVzJ13</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>centonze fabien</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>vLPNfRe2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>coco marcus</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>l2t9fvR7</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>mahamoud adel</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pQ5GqXFF</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>locko bradley</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MoRIjLE2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>kone abdoul</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Y7pbUJA4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>al tamari mousa suleiman</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bkWk025d</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>chotard joris</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2qMy8CA5</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>coulibaly tanguy</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>pA3wMl0B</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>issoufou yanis ali</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4hOup61a</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>jullien christopher</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>OEsM5Dqs</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>maamma othmane</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A1rzEd2O</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>inzingoula rabby</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>G8o32H2s</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>sainte luce theo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ye5BXk1R</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>bellaarouch alaa</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>KIP4iWK5</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cabot jimmy</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>f3mqZ2x6</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>el aynaoui neil</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>00OiLLms</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>labeau remy</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2qEVnrLJ</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ojediran hamzat</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>rmhmN1WA</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>satriano martin</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>pdcd6LXR</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>zaroury anass</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Q1kigul6</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>bard melvin</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>KdLy7rKC</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>laborde gaetan</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ny2HpVKp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>moffi teremas</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>x2fvnkud</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hernandez lucas</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dMyiR1D8</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>kimpembe presnel</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>xfW2M1Tt</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ramos goncalo</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>n5LaWeHr</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>sanson morgan</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AA15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,201 +441,185 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_8</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_8</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_9</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_9</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_3</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_4</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_4</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_6</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_6</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_7</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_7</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_8</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_8</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xYNVFHvB</t>
+          <t>IHSe3ve5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MkgjOoBG</t>
+          <t>I3i2lcHS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kone ismael</t>
+          <t>molebe enzo</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>jXMIit0S</t>
+          <t>hYtVzJ13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>moumbagna faris</t>
+          <t>centonze fabien</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2TItKacj</t>
+          <t>vLPNfRe2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nadir bilal</t>
+          <t>coco marcus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>tSVHHLjn</t>
+          <t>21Ny44li</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>cherif sidiki</t>
+          <t>lepenant johann</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ba2ejA41</t>
+          <t>l2t9fvR7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>dieng bamba cheikh dieng</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>WdtzR8gp</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>kalumba justin noel</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>SdIAUhSt</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>lopy joseph</t>
-        </is>
-      </c>
+          <t>mahamoud adel</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -652,91 +636,51 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>z9REJaun</t>
+          <t>rZUMHwAb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KKGaeL7f</t>
+          <t>pQ5GqXFF</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>briancon anthony</t>
+          <t>locko bradley</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>67mIaVqd</t>
+          <t>dbewx0xU</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>cornud pierre</t>
+          <t>kitala yann</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>by5QHeY8</t>
+          <t>6H79Cl3d</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>macon yvann</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>vJSrWUkm</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>agouzoul saad</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>W0j88M7O</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>coulibaly lasso</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>UZG5ZtWh</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>n gatta ange</t>
-        </is>
-      </c>
+          <t>mosengo daren nbenbege</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>OlWkr4He</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>monconduit thomas</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>vswx9zEb</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wadji ibrahima</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
@@ -749,63 +693,119 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Wf14adfU</t>
+          <t>WhWcJjo3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UVRm5Kjk</t>
+          <t>YywLL7YO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bentaleb nabil</t>
+          <t>gabriel moscardo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UZDgIuNN</t>
+          <t>Y7pbUJA4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>haraldsson hakon arnar</t>
+          <t>al tamari mousa suleiman</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>OADlCrGQ</t>
+          <t>bkWk025d</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>mbappe ethan</t>
+          <t>chotard joris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>rNvzndzO</t>
+          <t>2qMy8CA5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>wasbauer nicolas</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+          <t>coulibaly tanguy</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>pA3wMl0B</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>issoufou yanis ali</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MoRIjLE2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>kone abdoul</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4hOup61a</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>jullien christopher</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ERFuKxAR</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>kouyate boubakar</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>OEsM5Dqs</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>maamma othmane</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>A1rzEd2O</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>inzingoula rabby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>G8o32H2s</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>sainte luce theo</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
@@ -814,84 +814,164 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8Kp3c9Oq</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ye5BXk1R</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bellaarouch alaa</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>KIP4iWK5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>cabot jimmy</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>f3mqZ2x6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>el aynaoui neil</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2yi87XSs</t>
+          <t>00OiLLms</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>coulibaly mamadou</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+          <t>labeau remy</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2qEVnrLJ</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ojediran hamzat</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>h2cuSnsi</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>sarr mamadou</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>rmhmN1WA</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>satriano martin</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>pdcd6LXR</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>zaroury anass</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>YFqLAlLI</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>senaya marvin</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Q1kigul6</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bard melvin</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>x2fvnkud</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>hernandez lucas</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>dMyiR1D8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>kimpembe presnel</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>hYtVzJ13</t>
+          <t>xfW2M1Tt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>centonze fabien</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>vLPNfRe2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>coco marcus</t>
-        </is>
-      </c>
+          <t>ramos goncalo</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>l2t9fvR7</t>
+          <t>KdLy7rKC</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>mahamoud adel</t>
+          <t>laborde gaetan</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -904,27 +984,35 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>ny2HpVKp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>moffi teremas</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>n5LaWeHr</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>sanson morgan</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>pQ5GqXFF</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>locko bradley</t>
-        </is>
-      </c>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
@@ -953,192 +1041,64 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MoRIjLE2</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>kone abdoul</t>
-        </is>
-      </c>
+          <t>WzwSMPie</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Y7pbUJA4</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>al tamari mousa suleiman</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bkWk025d</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>chotard joris</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2qMy8CA5</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>coulibaly tanguy</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>pA3wMl0B</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>issoufou yanis ali</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>4hOup61a</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>jullien christopher</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>OEsM5Dqs</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>maamma othmane</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>A1rzEd2O</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>inzingoula rabby</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>G8o32H2s</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>sainte luce theo</t>
-        </is>
-      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ye5BXk1R</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>bellaarouch alaa</t>
-        </is>
-      </c>
+          <t>OAZJOoNr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>KIP4iWK5</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>cabot jimmy</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>f3mqZ2x6</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>el aynaoui neil</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>00OiLLms</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>labeau remy</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2qEVnrLJ</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>ojediran hamzat</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>rmhmN1WA</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>satriano martin</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>pdcd6LXR</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>zaroury anass</t>
-        </is>
-      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
@@ -1147,81 +1107,25 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Q1kigul6</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>bard melvin</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>KdLy7rKC</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>laborde gaetan</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ny2HpVKp</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>moffi teremas</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>x2fvnkud</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>hernandez lucas</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>dMyiR1D8</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>kimpembe presnel</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>xfW2M1Tt</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ramos goncalo</t>
-        </is>
-      </c>
+          <t>S2WzL3M7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>n5LaWeHr</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>sanson morgan</t>
-        </is>
-      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1236,7 +1140,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -1266,6 +1170,138 @@
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>h8K6HUFF</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WMcg8Qx2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vPIEF8pS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>nVutWTU8</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,15 +425,165 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>vwbmU7aL</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>YPYwQXje</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>andre benjamin</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>UVRm5Kjk</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>bentaleb nabil</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +591,36 @@
           <t>WzwSMPie</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>pQ5GqXFF</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>locko bradley</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +628,116 @@
           <t>OAZJOoNr</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KIP4iWK5</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>cabot jimmy</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>f3mqZ2x6</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>el aynaoui neil</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KKGaeL7f</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>briancon anthony</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>67mIaVqd</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cornud pierre</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>by5QHeY8</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>macon yvann</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>OlWkr4He</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>monconduit thomas</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>vswx9zEb</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>wadji ibrahima</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>dtKPzgw3</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>gradit jonathan</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>zchMcMs2</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>koffi herve</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2qEVnrLJ</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>ojediran hamzat</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>rmhmN1WA</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>satriano martin</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +745,100 @@
           <t>S2WzL3M7</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ye5BXk1R</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bellaarouch alaa</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>rcZfwzkD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sahi dion</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>x2fvnkud</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>hernandez lucas</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>dMyiR1D8</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>kimpembe presnel</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>xfW2M1Tt</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ramos goncalo</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>hjJue7Qt</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>lukovic milos</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>h2cuSnsi</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>sarr mamadou</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>YFqLAlLI</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>senaya marvin</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>ARPvetaS</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>wiley caleb</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +846,28 @@
           <t>b9aoAn8k</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +875,28 @@
           <t>h8K6HUFF</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +904,28 @@
           <t>WMcg8Qx2</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +933,28 @@
           <t>vPIEF8pS</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +962,28 @@
           <t>nVutWTU8</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -497,6 +991,28 @@
           <t>lYpTkOLs</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -504,6 +1020,28 @@
           <t>p0vxl2jf</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -511,6 +1049,28 @@
           <t>hQspntL6</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -518,6 +1078,28 @@
           <t>vaZNtoqR</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -525,6 +1107,28 @@
           <t>WdE2Z2y1</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -532,6 +1136,28 @@
           <t>vNHAXt6D</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -539,6 +1165,28 @@
           <t>KdJMr7EE</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -546,6 +1194,28 @@
           <t>h2acepbK</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -553,6 +1223,28 @@
           <t>AsQgyP6l</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -846,24 +846,72 @@
           <t>b9aoAn8k</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>vm0eu2V3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cherki mathis</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>I3i2lcHS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>molebe enzo</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>dbewx0xU</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>kitala yann</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6H79Cl3d</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>mosengo daren nbenbege</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>K8mhV4Es</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>gift emmanuel</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>YHEohwp4</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>zaha wilfried</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,80 +425,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:AG6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
@@ -521,778 +521,725 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_8</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_8</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_5</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_5</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_6</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_9</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_9</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YPYwQXje</t>
+          <t>WvnBSOGB</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>andre benjamin</t>
+          <t>youte kinkoue etienne</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>UVRm5Kjk</t>
+          <t>A3L0pzbI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>bentaleb nabil</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+          <t>casimir josue</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>dbewx0xU</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>kitala yann</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>4GZwFq7E</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>logbo andy elysee</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6H79Cl3d</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>mosengo daren nbenbege</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>K44QNA2A</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>caleta car duje</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>6PvHspma</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>clinton mata</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Kty10JVG</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>matic nemanja</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>I3i2lcHS</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>molebe enzo</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WzwSMPie</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>h8K6HUFF</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>W0j88M7O</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>coulibaly lasso</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2TDOiuxH</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>owusu elisha</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pQ5GqXFF</t>
+          <t>vJSrWUkm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>locko bradley</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+          <t>agouzoul saad</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>rcA08ag8</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>camara ousoumane</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4b1ioyMB</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>jubal</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>tSf0YZjE</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>khadra reda</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>YywLL7YO</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>gabriel moscardo</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>MoRIjLE2</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>kone abdoul</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>UZG5ZtWh</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>n gatta ange</t>
+        </is>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OAZJOoNr</t>
+          <t>WMcg8Qx2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KIP4iWK5</t>
+          <t>AsPIAoni</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cabot jimmy</t>
+          <t>augusto douglas</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>f3mqZ2x6</t>
+          <t>hYtVzJ13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>el aynaoui neil</t>
+          <t>centonze fabien</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KKGaeL7f</t>
+          <t>vLPNfRe2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>briancon anthony</t>
+          <t>coco marcus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>67mIaVqd</t>
+          <t>l2t9fvR7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>cornud pierre</t>
+          <t>mahamoud adel</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>by5QHeY8</t>
+          <t>MiH8I5Na</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>macon yvann</t>
+          <t>castelletto jean charles</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>OlWkr4He</t>
+          <t>nNPcDNFr</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>monconduit thomas</t>
+          <t>dante</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>vswx9zEb</t>
+          <t>ny2HpVKp</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>wadji ibrahima</t>
+          <t>moffi teremas</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>dtKPzgw3</t>
+          <t>GEIWE1pD</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>gradit jonathan</t>
+          <t>ndombele tanguy</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>zchMcMs2</t>
+          <t>Q1kigul6</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>koffi herve</t>
+          <t>bard melvin</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2qEVnrLJ</t>
+          <t>G6Icx4DR</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>ojediran hamzat</t>
+          <t>duverne jean kevin</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>rmhmN1WA</t>
+          <t>AiotaxUt</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>satriano martin</t>
-        </is>
-      </c>
+          <t>guirassy bahereba</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0vxfG1Jf</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>kadewere tino</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>6acylKhj</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>ndayishimiye youssouf</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>n5LaWeHr</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>sanson morgan</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>S2WzL3M7</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ye5BXk1R</t>
+          <t>4UatnyW3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bellaarouch alaa</t>
+          <t>casseres cristian</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>rcZfwzkD</t>
+          <t>d2T8jid4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sahi dion</t>
+          <t>donnum aron</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>x2fvnkud</t>
+          <t>4vagAHJd</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>hernandez lucas</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>dMyiR1D8</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>kimpembe presnel</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>xfW2M1Tt</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>ramos goncalo</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+          <t>nicolaisen rasmus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>WdtzR8gp</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>kalumba justin noel</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>dlgWt8kH</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>rao lisoa lilian</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>hjJue7Qt</t>
+          <t>tSVHHLjn</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>lukovic milos</t>
+          <t>cherif sidiki</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>h2cuSnsi</t>
+          <t>ba2ejA41</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>sarr mamadou</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>YFqLAlLI</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>senaya marvin</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>ARPvetaS</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>wiley caleb</t>
-        </is>
-      </c>
+          <t>dieng bamba cheikh dieng</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>hA8XZuUp</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>ferhat zinedine</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>SdIAUhSt</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>lopy joseph</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>nVutWTU8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>vm0eu2V3</t>
+          <t>pA3wMl0B</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cherki mathis</t>
+          <t>issoufou yanis ali</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>I3i2lcHS</t>
+          <t>4hOup61a</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>molebe enzo</t>
+          <t>jullien christopher</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>dbewx0xU</t>
+          <t>ERFuKxAR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>kitala yann</t>
+          <t>kouyate boubakar</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6H79Cl3d</t>
+          <t>pYI2rM4H</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>mosengo daren nbenbege</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+          <t>sagnan modibo</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Y7pbUJA4</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>al tamari mousa suleiman</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0S6Hz5ji</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>carboni valentin</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>d0bSRUiP</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>maupay neal</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>K8mhV4Es</t>
+          <t>jXMIit0S</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>gift emmanuel</t>
+          <t>moumbagna faris</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>YHEohwp4</t>
+          <t>4WfxXiUm</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>zaha wilfried</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>h8K6HUFF</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>WMcg8Qx2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>vPIEF8pS</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>nVutWTU8</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>lYpTkOLs</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>p0vxl2jf</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>hQspntL6</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>vaZNtoqR</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WdE2Z2y1</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>vNHAXt6D</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>KdJMr7EE</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>h2acepbK</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>AsQgyP6l</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+          <t>blanco ruben</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>j5dSkdZI</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>ferri jordan</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>dSDrHenE</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>gueguin axel</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>OEsM5Dqs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>maamma othmane</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>MkgjOoBG</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>kone ismael</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>tvuaMWgc</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>merlin quentin</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>G8o32H2s</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>sainte luce theo</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>2TItKacj</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>nadir bilal</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,15 +425,305 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A19"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_8</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_8</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_8</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_8</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_9</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_9</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_9</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_9</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>lYpTkOLs</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CngQQtwt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>alemdar dogan</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>8EP6jKUI</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>meister henrik</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>lIN7BM8b</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ostigard leo</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>6H79Cl3d</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>mosengo daren nbenbege</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>hzxA3Bvf</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>el hajjam oualid</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>n5pKaQsh</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>joujou antoine</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>dbewx0xU</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>kitala yann</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4GZwFq7E</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>logbo andy elysee</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>lGwSlg7D</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>sangante arouna</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +731,146 @@
           <t>p0vxl2jf</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fL3dsspB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>belkebla haris</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>f9CImc7o</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ekomie jacques</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>dpU7jLLp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>hountondji cedric</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>KKGaeL7f</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>briancon anthony</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>67mIaVqd</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>cornud pierre</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>by5QHeY8</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>macon yvann</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>OlWkr4He</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>monconduit thomas</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>vswx9zEb</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>wadji ibrahima</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>WdtzR8gp</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>kalumba justin noel</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>dlgWt8kH</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>rao lisoa lilian</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>tSVHHLjn</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>cherif sidiki</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>hA8XZuUp</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>ferhat zinedine</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>SdIAUhSt</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>lopy joseph</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +878,74 @@
           <t>hQspntL6</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>63FSiIkD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>daramy mohammed</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>tSf0YZjE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>khadra reda</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>hEHAtkEC</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>le cardinal julien</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>pQ5GqXFF</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>locko bradley</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +953,178 @@
           <t>vaZNtoqR</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Of80t1aH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>aguilar ruben</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>KIP4iWK5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>cabot jimmy</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>zchMcMs2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>koffi herve</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>zB5OlUKE</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>bakker mitchel</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>UVRm5Kjk</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>bentaleb nabil</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>dpoNasPg</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bouaddi ayyoub</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>hl6k3P1f</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>cabella remy</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>UZDgIuNN</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>haraldsson hakon arnar</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>neNU9A9F</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>ismaily</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CSjPEukJ</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>machado deiver</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2qEVnrLJ</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>ojediran hamzat</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>400jX4xg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>said wesley</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>rmhmN1WA</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>satriano martin</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>f3mqZ2x6</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>el aynaoui neil</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>OADlCrGQ</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>mbappe ethan</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>vBypn8GA</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>santos tiago</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>zsH7aMfI</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>umtiti samuel</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +1132,90 @@
           <t>WdE2Z2y1</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>WG2O5tgf</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>diawara mahamadou</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Kty10JVG</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>matic nemanja</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>I3i2lcHS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>molebe enzo</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>W0j88M7O</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>coulibaly lasso</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bNxDifo4</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>joly paul</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>vJSrWUkm</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>agouzoul saad</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +1223,122 @@
           <t>vNHAXt6D</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>S4sVF7O0</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>dzodic stefan</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Qwp5yt4r</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>fayad khalil</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>pA3wMl0B</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>issoufou yanis ali</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4vagAHJd</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>nicolaisen rasmus</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4hOup61a</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>jullien christopher</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>ERFuKxAR</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>kouyate boubakar</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Y7pbUJA4</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>al tamari mousa suleiman</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>bkWk025d</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>chotard joris</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>OEsM5Dqs</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>maamma othmane</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>G8o32H2s</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>sainte luce theo</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +1346,122 @@
           <t>KdJMr7EE</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Q1kigul6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bard melvin</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ny2HpVKp</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>moffi teremas</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>GEIWE1pD</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ndombele tanguy</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>rVZLmUsU</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>balgun folarin</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2yi87XSs</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>coulibaly mamadou</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>EJpPkLtD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>diop edan</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Sbk0VFPJ</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>teze jordan</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>n5LaWeHr</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>sanson morgan</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>xOd4FVMQ</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>cho mohamed ali</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>6acylKhj</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>ndayishimiye youssouf</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +1469,122 @@
           <t>h2acepbK</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ye5BXk1R</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>bellaarouch alaa</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>tvY8ZVkb</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>delaine thomas</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>rcZfwzkD</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>sahi dion</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>hYtVzJ13</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>centonze fabien</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>l2t9fvR7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>mahamoud adel</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>G6Icx4DR</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>duverne jean kevin</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>AiotaxUt</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>guirassy bahereba</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>by8Xcffd</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>emegha emanuel</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>hjJue7Qt</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>lukovic milos</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>ARPvetaS</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>wiley caleb</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,69 +1592,98 @@
           <t>AsQgyP6l</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>0ljCkFRb</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>bqYbtBlo</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>rX720WuH</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>n5Eg2hB4</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>vuBo4Eth</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>4Md3iycn</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>EuWhpKkJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Y1lKmgdB</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>UTsToXQN</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0S6Hz5ji</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>carboni valentin</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>jXMIit0S</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>moumbagna faris</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4WfxXiUm</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>blanco ruben</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>x2fvnkud</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hernandez lucas</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dMyiR1D8</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>kimpembe presnel</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>xfW2M1Tt</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ramos goncalo</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2TItKacj</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>nadir bilal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,15 +425,389 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A19"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_8</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_8</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_8</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_8</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_9</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_9</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_9</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_9</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_10</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_10</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_11</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_11</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_12</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_12</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>0ljCkFRb</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>rVZLmUsU</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>balgun folarin</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2yi87XSs</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>coulibaly mamadou</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>EJpPkLtD</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>diop edan</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>zuFTjQI5</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>salisu mohammed</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Sbk0VFPJ</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teze jordan</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>OjKXB6ns</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>vanderson</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>d23lOQrL</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>zakaria denis</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>tSVHHLjn</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>cherif sidiki</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>hA8XZuUp</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>ferhat zinedine</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>dpU7jLLp</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>hountondji cedric</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>WdtzR8gp</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>kalumba justin noel</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>SdIAUhSt</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>lopy joseph</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>dlgWt8kH</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>rao lisoa lilian</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>ba2ejA41</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>dieng bamba cheikh dieng</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>f9CImc7o</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>ekomie jacques</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +815,152 @@
           <t>bqYbtBlo</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>6kFjexWI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>alexsandro</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>UVRm5Kjk</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>bentaleb nabil</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hl6k3P1f</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>cabella remy</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>dd9HmQlk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>fernandes rafael</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>UZDgIuNN</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>haraldsson hakon arnar</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>neNU9A9F</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ismaily</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>OADlCrGQ</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>mbappe ethan</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>WG2O5tgf</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>diawara mahamadou</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>rsiloRPO</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>nuamah ernest</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>K8mhV4Es</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>gift emmanuel</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>QgN9t9CH</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>mikautadze georges</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>vBypn8GA</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>santos tiago</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>zsH7aMfI</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>umtiti samuel</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +968,152 @@
           <t>rX720WuH</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Y1UU1rz7</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>lucas beraldo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>x2fvnkud</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>hernandez lucas</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>dMyiR1D8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>kimpembe presnel</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>xfW2M1Tt</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ramos goncalo</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Of80t1aH</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>aguilar ruben</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>KIP4iWK5</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>cabot jimmy</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>ILw1CMMs</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>fulgini angelo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>zchMcMs2</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>koffi herve</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>tEuOUQT3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>medina facundo</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>400jX4xg</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>said wesley</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>rmhmN1WA</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>satriano martin</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>IiBJCs82</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>diouf andy</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>jwOj3L3C</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>frankowski przemyslaw</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +1121,120 @@
           <t>n5Eg2hB4</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pQ5GqXFF</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>locko bradley</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>xzssoNnp</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sima abdallah</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>bmj4mkKq</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>luc zogbe</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>URcBI8WC</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>boudaoui hichem</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ny2HpVKp</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>moffi teremas</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Ag37eHIn</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>clauss jonathan</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>6acylKhj</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>ndayishimiye youssouf</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>GEIWE1pD</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>ndombele tanguy</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>n5LaWeHr</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>sanson morgan</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +1242,152 @@
           <t>vuBo4Eth</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>KKGaeL7f</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>briancon anthony</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>OlWkr4He</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>monconduit thomas</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>4MoD7F1A</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>old benjamin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>67mIaVqd</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cornud pierre</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>by5QHeY8</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>macon yvann</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>vswx9zEb</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>wadji ibrahima</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>by8Xcffd</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>emegha emanuel</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>hjJue7Qt</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>lukovic milos</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>YFqLAlLI</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>senaya marvin</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ye5BXk1R</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>bellaarouch alaa</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>tvY8ZVkb</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delaine thomas</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>rcZfwzkD</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>sahi dion</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>ARPvetaS</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>wiley caleb</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +1395,104 @@
           <t>4Md3iycn</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4vagAHJd</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>nicolaisen rasmus</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SvBsKAPE</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>buta aurelio</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>63FSiIkD</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>daramy mohammed</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>tSf0YZjE</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>khadra reda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2LonY10K</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>munetsi nyasha</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>pWuFUK4s</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>teuma teddy</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>MoRIjLE2</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>kone abdoul</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +1500,120 @@
           <t>EuWhpKkJ</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rcA08ag8</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>camara ousoumane</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>W0j88M7O</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>coulibaly lasso</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>bNxDifo4</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>joly paul</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vJSrWUkm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>agouzoul saad</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CtMie175</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>osho gabriel</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Sr1MZT2U</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>traore hamed</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CngQQtwt</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>alemdar dogan</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>bi8NhkWD</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>seidu alidu</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>8EP6jKUI</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>meister henrik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +1621,216 @@
           <t>Y1lKmgdB</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A3L0pzbI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>casimir josue</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>hzxA3Bvf</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>el hajjam oualid</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>n5pKaQsh</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>joujou antoine</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>dbewx0xU</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>kitala yann</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>AgmwPJ36</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>kuzyayev daler</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>4GZwFq7E</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>logbo andy elysee</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>6H79Cl3d</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>mosengo daren nbenbege</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>S4sVF7O0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>dzodic stefan</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>pA3wMl0B</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>issoufou yanis ali</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4hOup61a</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>jullien christopher</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>ERFuKxAR</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>kouyate boubakar</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>hQGrDm2I</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>omeragic becir</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>vsv6TioJ</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>savanier teji</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Y7pbUJA4</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>al tamari mousa suleiman</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>bkWk025d</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>chotard joris</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>lIu2iTW5</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>operi christopher</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>lGwSlg7D</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>sangante arouna</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Qwp5yt4r</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>fayad khalil</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>OEsM5Dqs</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>maamma othmane</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>2q9g9abc</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>maksimovic nikola</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>G8o32H2s</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>sainte luce theo</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,69 +1838,136 @@
           <t>UTsToXQN</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Gp6AbAAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>figxD9PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>bJl87mmp</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dYK8BH5F</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>l8H0Dwy3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>nRkUEVfA</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QB1LGiQc</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>WWnG5RHd</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>b59ZhlYj</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>hYtVzJ13</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>centonze fabien</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>21Ny44li</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>lepenant johann</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>l2t9fvR7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>mahamoud adel</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0S6Hz5ji</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>carboni valentin</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>lxSgSRDd</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>harit amine</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>U5hu6oJh</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>mbemba chancel</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>jXMIit0S</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>moumbagna faris</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4WfxXiUm</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>blanco ruben</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2Rrnmrcp</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>garcia ulisses</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>tvuaMWgc</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>merlin quentin</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2TItKacj</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>nadir bilal</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,15 +425,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A10"/>
+  <dimension ref="A1:AG14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_8</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_8</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_9</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_9</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Gp6AbAAT</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>4WfxXiUm</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>blanco ruben</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0S6Hz5ji</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>carboni valentin</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>U5hu6oJh</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>mbemba chancel</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>jXMIit0S</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>moumbagna faris</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2Rrnmrcp</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>garcia ulisses</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2TItKacj</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>nadir bilal</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>vJSrWUkm</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>agouzoul saad</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>W0j88M7O</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>coulibaly lasso</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>6X2uao2q</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>diomande sinaly</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>bNxDifo4</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>joly paul</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>4b1ioyMB</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>jubal</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>UZG5ZtWh</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>n gatta ange</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>rcA08ag8</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>camara ousoumane</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +739,126 @@
           <t>figxD9PM</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ye5BXk1R</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bellaarouch alaa</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>tvY8ZVkb</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>delaine thomas</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>rcZfwzkD</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>sahi dion</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>by8Xcffd</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>emegha emanuel</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Op4InIJ1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>sebas jeremy</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>YFqLAlLI</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>senaya marvin</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>rVZLmUsU</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>balgun folarin</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2yi87XSs</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>coulibaly mamadou</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>EJpPkLtD</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>diop edan</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>zuFTjQI5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>salisu mohammed</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>d23lOQrL</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>zakaria denis</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +866,142 @@
           <t>bJl87mmp</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Of80t1aH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>aguilar ruben</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>KIP4iWK5</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>cabot jimmy</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>00ElbXx5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>khusanov abdukodir</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vD33dp4n</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>nzola m bala</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>400jX4xg</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>said wesley</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>rmhmN1WA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>satriano martin</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>hYtVzJ13</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>centonze fabien</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>l2t9fvR7</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>mahamoud adel</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>xYHsz2uS</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>zeze nathan</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>21Ny44li</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>lepenant johann</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>ILw1CMMs</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>fulgini angelo</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>zchMcMs2</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>koffi herve</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>AgROGWlt</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>sotoca florian</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +1009,102 @@
           <t>dYK8BH5F</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>WdtzR8gp</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>kalumba justin noel</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>tSVHHLjn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>cherif sidiki</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hA8XZuUp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ferhat zinedine</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>dpU7jLLp</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>hountondji cedric</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SdIAUhSt</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>lopy joseph</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>x2fvnkud</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>hernandez lucas</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>dMyiR1D8</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>kimpembe presnel</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>xfW2M1Tt</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>ramos goncalo</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +1112,118 @@
           <t>l8H0Dwy3</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>URcBI8WC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>boudaoui hichem</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ny2HpVKp</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>moffi teremas</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>n5LaWeHr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>sanson morgan</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>hl6k3P1f</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>cabella remy</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>dd9HmQlk</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>fernandes rafael</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>neNU9A9F</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>ismaily</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>OADlCrGQ</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>mbappe ethan</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>WUyrShAL</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>meunier thomas</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>vBypn8GA</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>santos tiago</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0l0PGXES</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>toure ousmane</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +1231,110 @@
           <t>nRkUEVfA</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hzxA3Bvf</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>el hajjam oualid</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>dbewx0xU</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>kitala yann</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4GZwFq7E</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>logbo andy elysee</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6H79Cl3d</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>mosengo daren nbenbege</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2FPUx4e9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ngoura steve</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>lGwSlg7D</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>sangante arouna</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>63FSiIkD</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>daramy mohammed</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>tSf0YZjE</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>khadra reda</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>pWuFUK4s</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>teuma teddy</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +1342,134 @@
           <t>QB1LGiQc</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S4sVF7O0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>dzodic stefan</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>pA3wMl0B</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>issoufou yanis ali</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4hOup61a</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>jullien christopher</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ERFuKxAR</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>kouyate boubakar</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>hQGrDm2I</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>omeragic becir</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>vsv6TioJ</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>savanier teji</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>pQ5GqXFF</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>locko bradley</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>xzssoNnp</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>sima abdallah</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>bmj4mkKq</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>luc zogbe</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>bkWk025d</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>chotard joris</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Qwp5yt4r</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>fayad khalil</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>G8o32H2s</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>sainte luce theo</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +1477,54 @@
           <t>WWnG5RHd</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CngQQtwt</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>alemdar dogan</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4vagAHJd</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>nicolaisen rasmus</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +1532,258 @@
           <t>b59ZhlYj</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kty10JVG</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>matic nemanja</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>rsiloRPO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>nuamah ernest</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>KKGaeL7f</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>briancon anthony</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>dKzjZfiI</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>cafaro mathieu</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>OlWkr4He</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>monconduit thomas</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>4MoD7F1A</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>old benjamin</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>67mIaVqd</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>cornud pierre</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>vswx9zEb</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>wadji ibrahima</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xdpX3Q36</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Im9H9ezS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SMfm4Zck</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GryrQGK8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
